--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_HAMPSHIRE_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/NEW_HAMPSHIRE_2020.xlsx
@@ -1057,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>0.09677419354838709</v>
+        <v>0.09677419354838708</v>
       </c>
     </row>
   </sheetData>
